--- a/src/context/inventario/INVENTARIO MARZO 2026.xlsx
+++ b/src/context/inventario/INVENTARIO MARZO 2026.xlsx
@@ -2254,7 +2254,7 @@
         <v>80000</v>
       </c>
       <c r="I64" t="str">
-        <v>https://jaltechsas.com/wp-content/uploads/2023/11/CARG.-PARA-ASUS-19V-1.75_80300_BSK-AS03_1.png</v>
+        <v>https://jaltechsas.com/wp-content/uploads/2023/11/CARG.-PARA-ASUS-19V-1.75_80300_BSK-AS03_1.png?row=62</v>
       </c>
     </row>
     <row r="65">
@@ -5821,7 +5821,7 @@
         <v>100000</v>
       </c>
       <c r="I187" t="str">
-        <v>https://jaltechsas.com/wp-content/uploads/2023/03/FUENTE-DE-PODER-230W-REALES_11298_-FPS-230W_1.png</v>
+        <v>https://jaltechsas.com/wp-content/uploads/2023/03/FUENTE-DE-PODER-230W-REALES_11298_-FPS-230W_1.png?row=185</v>
       </c>
     </row>
     <row r="188">
@@ -5937,7 +5937,7 @@
         <v>45000</v>
       </c>
       <c r="I191" t="str">
-        <v>http://www.goditek.com/cdn/shop/files/SWITCH-PLUS-5-PUERTOS-BASE-100---JAL-PS5_11646_JAL-PS5_1_1200x1200.png?v=1751043231</v>
+        <v>http://www.goditek.com/cdn/shop/files/SWITCH-PLUS-5-PUERTOS-BASE-100---JAL-PS5_11646_JAL-PS5_1_1200x1200.png?v=1751043231&amp;row=189</v>
       </c>
     </row>
     <row r="192">
@@ -10577,7 +10577,7 @@
         <v>58000</v>
       </c>
       <c r="I351" t="str">
-        <v>https://trivico.la/images/products/detail/HP-19V-1.58A-4.0x1.7-OEM-NBC111.jpg</v>
+        <v>https://trivico.la/images/products/detail/HP-19V-1.58A-4.0x1.7-OEM-NBC111.jpg?row=349</v>
       </c>
     </row>
     <row r="352">
@@ -11502,7 +11502,7 @@
         <v>10000</v>
       </c>
       <c r="I383" t="str">
-        <v>https://http2.mlstatic.com/D_NQ_NP_806843-MLA84848804699_052025-O.webp</v>
+        <v>https://http2.mlstatic.com/D_NQ_NP_806843-MLA84848804699_052025-O.webp?row=381</v>
       </c>
     </row>
     <row r="384">
@@ -13444,7 +13444,7 @@
         <v>80000</v>
       </c>
       <c r="I451" t="str">
-        <v>https://jaltechsas.com/wp-content/uploads/2024/09/MICROFONO TX DE SOLAPA TIPO C_30699_F9-TC_2.png</v>
+        <v>https://jaltechsas.com/wp-content/uploads/2024/09/MICROFONO TX DE SOLAPA TIPO C_30699_F9-TC_2.png?row=449</v>
       </c>
     </row>
     <row r="452">
@@ -14401,7 +14401,7 @@
         <v>20000</v>
       </c>
       <c r="I484" t="str">
-        <v>https://http2.mlstatic.com/D_NQ_NP_821560-MLC72703805656_112023-O-cable-mini-hdmi-a-hdmi-largo-15-metros.webp</v>
+        <v>https://http2.mlstatic.com/D_NQ_NP_821560-MLC72703805656_112023-O-cable-mini-hdmi-a-hdmi-largo-15-metros.webp?row=482</v>
       </c>
     </row>
     <row r="485">
